--- a/data/trans_orig/IP19C05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85526</t>
+          <t>86312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>223243</t>
+          <t>222677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227721</t>
+          <t>227727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237936</t>
+          <t>237718</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244391</t>
+          <t>244387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463507</t>
+          <t>463779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471389</t>
+          <t>471477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72807</t>
+          <t>72495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145628</t>
+          <t>145238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,47 +1776,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7925</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343090</t>
+          <t>343477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349664</t>
+          <t>349693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,49 +1889,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>353223</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>360432</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>353806</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>360414</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1057</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700022</t>
+          <t>700021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708970</t>
+          <t>709156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44070</t>
+          <t>44119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86915</t>
+          <t>87032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211876</t>
+          <t>212529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219038</t>
+          <t>219020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232533</t>
+          <t>232763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238964</t>
+          <t>239448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447656</t>
+          <t>446948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>457312</t>
+          <t>456979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76936</t>
+          <t>76190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83946</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76159</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81473</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156226</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164633</t>
+          <t>164485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>338781</t>
+          <t>338143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348967</t>
+          <t>348732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>354820</t>
+          <t>354383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363162</t>
+          <t>363154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696723</t>
+          <t>697157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710096</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19773</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239918</t>
+          <t>239828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249361</t>
+          <t>249139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243206</t>
+          <t>243169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250566</t>
+          <t>250587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>486233</t>
+          <t>486458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498192</t>
+          <t>498343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82502</t>
+          <t>81334</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87084</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167864</t>
+          <t>168445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174106</t>
+          <t>174198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347580</t>
+          <t>346373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357703</t>
+          <t>357356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356614</t>
+          <t>356304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365080</t>
+          <t>365149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707587</t>
+          <t>707595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720602</t>
+          <t>721589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4607</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4855</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4348</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3504</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46053</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42319</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42071</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>133</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86312</t>
+          <t>85468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8139</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1882</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5645</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4996</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8005</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>9766</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5413</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>10266</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>242191</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>237584</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>244333</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>226440</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>222677</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>227727</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>223326</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>227726</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>242191</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>237718</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>244387</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>707</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463779</t>
+          <t>464279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471477</t>
+          <t>471478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3562</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75051</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72495</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71909</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145238</t>
+          <t>145637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,52 +1639,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7453</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8508</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1864,67 +1864,67 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>353796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>360400</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>347543</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>343477</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>349693</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>343581</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>349675</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>353223</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>360432</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700021</t>
+          <t>700248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>709156</t>
+          <t>709234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3896</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46699</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44119</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43519</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>126</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87032</t>
+          <t>87027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8190</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3901</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7949</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4087</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>236826</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>232723</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>239463</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>216577</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>212529</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>219020</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>211360</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>218981</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>236826</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>232763</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>239448</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446948</t>
+          <t>447473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456979</t>
+          <t>457206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4120</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1610</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9358</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8530</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6209</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79994</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76879</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81472</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81428</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76190</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77018</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84120</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79994</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75916</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81467</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154934</t>
+          <t>155605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164485</t>
+          <t>164707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11351</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15848</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15840</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11619</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>359784</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>354651</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>363202</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>491</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>344705</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>338143</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>348732</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>338151</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>348662</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>359784</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>354383</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>363154</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697157</t>
+          <t>697090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710277</t>
+          <t>709793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,107 +3928,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2869</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21575</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19261</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19722</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>72</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8989</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7227</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3601</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12912</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3784</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13249</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4059</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9001</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>248111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>243181</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>250655</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>360</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>245513</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>239828</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>249139</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>239491</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>248956</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>248111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>243169</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>250587</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>486458</t>
+          <t>486835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498343</t>
+          <t>498272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1313</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4487</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6364</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85604</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82185</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87084</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>86427</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>83148</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83253</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85604</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81334</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87085</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>242</t>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168445</t>
+          <t>168283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174198</t>
+          <t>174675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11413</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9104</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5262</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16245</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5089</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15050</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11704</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>361855</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>356595</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>365568</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>514</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>353514</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>346373</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>357356</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>347568</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>357529</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>361855</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>356304</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>365149</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707595</t>
+          <t>707825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721589</t>
+          <t>720767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
